--- a/output/stock_quant_scores/ARM_income_df.xlsx
+++ b/output/stock_quant_scores/ARM_income_df.xlsx
@@ -1228,7 +1228,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>680000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1238,10 +1240,14 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>0.535059</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>549000000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
         <v>-156000000</v>
@@ -1266,9 +1272,13 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>2572000000</v>
+      </c>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>2703000000</v>
+      </c>
       <c r="AT6" t="inlineStr"/>
     </row>
   </sheetData>
